--- a/Team-Data/2008-09/5-8-2008-09.xlsx
+++ b/Team-Data/2008-09/5-8-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>5-8-2008-09</t>
+          <t>2009-05-08</t>
         </is>
       </c>
     </row>
@@ -843,25 +910,25 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E3" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F3" t="n">
         <v>20</v>
       </c>
       <c r="G3" t="n">
-        <v>0.753</v>
+        <v>0.756</v>
       </c>
       <c r="H3" t="n">
         <v>48.5</v>
       </c>
       <c r="I3" t="n">
-        <v>37.6</v>
+        <v>37.5</v>
       </c>
       <c r="J3" t="n">
-        <v>77.3</v>
+        <v>77.2</v>
       </c>
       <c r="K3" t="n">
         <v>0.486</v>
@@ -870,58 +937,58 @@
         <v>6.6</v>
       </c>
       <c r="M3" t="n">
-        <v>16.6</v>
+        <v>16.5</v>
       </c>
       <c r="N3" t="n">
-        <v>0.399</v>
+        <v>0.397</v>
       </c>
       <c r="O3" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="P3" t="n">
-        <v>25.2</v>
+        <v>25.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.767</v>
+        <v>0.765</v>
       </c>
       <c r="R3" t="n">
         <v>10.6</v>
       </c>
       <c r="S3" t="n">
-        <v>31.6</v>
+        <v>31.5</v>
       </c>
       <c r="T3" t="n">
-        <v>42.2</v>
+        <v>42.1</v>
       </c>
       <c r="U3" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="V3" t="n">
         <v>15.6</v>
       </c>
       <c r="W3" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="X3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Z3" t="n">
         <v>23.1</v>
       </c>
       <c r="AA3" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="AB3" t="n">
-        <v>101</v>
+        <v>100.9</v>
       </c>
       <c r="AC3" t="n">
         <v>7.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="AE3" t="n">
         <v>3</v>
@@ -957,46 +1024,46 @@
         <v>12</v>
       </c>
       <c r="AP3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AQ3" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AR3" t="n">
         <v>21</v>
       </c>
       <c r="AS3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AU3" t="n">
         <v>4</v>
       </c>
       <c r="AV3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AW3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AY3" t="n">
         <v>13</v>
       </c>
       <c r="AZ3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BA3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BB3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BD3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>5-8-2008-09</t>
+          <t>2009-05-08</t>
         </is>
       </c>
     </row>
@@ -1115,7 +1182,7 @@
         <v>19</v>
       </c>
       <c r="AH4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI4" t="n">
         <v>29</v>
@@ -1145,7 +1212,7 @@
         <v>27</v>
       </c>
       <c r="AR4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AS4" t="n">
         <v>25</v>
@@ -1157,7 +1224,7 @@
         <v>10</v>
       </c>
       <c r="AV4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AW4" t="n">
         <v>19</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>5-8-2008-09</t>
+          <t>2009-05-08</t>
         </is>
       </c>
     </row>
@@ -1207,28 +1274,28 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E5" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F5" t="n">
         <v>41</v>
       </c>
       <c r="G5" t="n">
-        <v>0.494</v>
+        <v>0.5</v>
       </c>
       <c r="H5" t="n">
         <v>48.6</v>
       </c>
       <c r="I5" t="n">
-        <v>38.2</v>
+        <v>38.1</v>
       </c>
       <c r="J5" t="n">
-        <v>83.7</v>
+        <v>83.5</v>
       </c>
       <c r="K5" t="n">
-        <v>0.456</v>
+        <v>0.457</v>
       </c>
       <c r="L5" t="n">
         <v>6</v>
@@ -1240,13 +1307,13 @@
         <v>0.381</v>
       </c>
       <c r="O5" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="P5" t="n">
-        <v>24.8</v>
+        <v>25</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.797</v>
+        <v>0.796</v>
       </c>
       <c r="R5" t="n">
         <v>11.8</v>
@@ -1258,7 +1325,7 @@
         <v>42.1</v>
       </c>
       <c r="U5" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="V5" t="n">
         <v>14.5</v>
@@ -1273,40 +1340,40 @@
         <v>5.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AB5" t="n">
-        <v>102.1</v>
+        <v>102.2</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.4</v>
+        <v>-0.3</v>
       </c>
       <c r="AD5" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="AE5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF5" t="n">
         <v>15</v>
       </c>
       <c r="AG5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH5" t="n">
         <v>2</v>
       </c>
       <c r="AI5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ5" t="n">
         <v>5</v>
       </c>
       <c r="AK5" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AL5" t="n">
         <v>22</v>
@@ -1318,7 +1385,7 @@
         <v>6</v>
       </c>
       <c r="AO5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AP5" t="n">
         <v>14</v>
@@ -1339,10 +1406,10 @@
         <v>13</v>
       </c>
       <c r="AV5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX5" t="n">
         <v>4</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>5-8-2008-09</t>
+          <t>2009-05-08</t>
         </is>
       </c>
     </row>
@@ -1389,43 +1456,43 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E6" t="n">
         <v>66</v>
       </c>
       <c r="F6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.805</v>
       </c>
       <c r="H6" t="n">
         <v>48.2</v>
       </c>
       <c r="I6" t="n">
-        <v>37</v>
+        <v>36.9</v>
       </c>
       <c r="J6" t="n">
-        <v>78.8</v>
+        <v>78.7</v>
       </c>
       <c r="K6" t="n">
-        <v>0.469</v>
+        <v>0.468</v>
       </c>
       <c r="L6" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="M6" t="n">
         <v>20.4</v>
       </c>
       <c r="N6" t="n">
-        <v>0.395</v>
+        <v>0.393</v>
       </c>
       <c r="O6" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="P6" t="n">
-        <v>24.4</v>
+        <v>24.5</v>
       </c>
       <c r="Q6" t="n">
         <v>0.757</v>
@@ -1443,7 +1510,7 @@
         <v>20.3</v>
       </c>
       <c r="V6" t="n">
-        <v>12.6</v>
+        <v>12.7</v>
       </c>
       <c r="W6" t="n">
         <v>7.2</v>
@@ -1452,22 +1519,22 @@
         <v>5.3</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Z6" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AB6" t="n">
-        <v>100.5</v>
+        <v>100.3</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.1</v>
+        <v>8.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1500,7 +1567,7 @@
         <v>2</v>
       </c>
       <c r="AO6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AP6" t="n">
         <v>15</v>
@@ -1521,16 +1588,16 @@
         <v>20</v>
       </c>
       <c r="AV6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AX6" t="n">
         <v>7</v>
       </c>
       <c r="AY6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ6" t="n">
         <v>9</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>5-8-2008-09</t>
+          <t>2009-05-08</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1731,7 @@
         <v>14</v>
       </c>
       <c r="AI7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AJ7" t="n">
         <v>6</v>
@@ -1703,7 +1770,7 @@
         <v>8</v>
       </c>
       <c r="AV7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW7" t="n">
         <v>17</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>5-8-2008-09</t>
+          <t>2009-05-08</t>
         </is>
       </c>
     </row>
@@ -1837,10 +1904,10 @@
         <v>5</v>
       </c>
       <c r="AF8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH8" t="n">
         <v>27</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>5-8-2008-09</t>
+          <t>2009-05-08</t>
         </is>
       </c>
     </row>
@@ -2076,7 +2143,7 @@
         <v>19</v>
       </c>
       <c r="AY9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AZ9" t="n">
         <v>19</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>5-8-2008-09</t>
+          <t>2009-05-08</t>
         </is>
       </c>
     </row>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>5-8-2008-09</t>
+          <t>2009-05-08</t>
         </is>
       </c>
     </row>
@@ -2410,7 +2477,7 @@
         <v>10</v>
       </c>
       <c r="AO11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP11" t="n">
         <v>21</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>5-8-2008-09</t>
+          <t>2009-05-08</t>
         </is>
       </c>
     </row>
@@ -2571,7 +2638,7 @@
         <v>18</v>
       </c>
       <c r="AH12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI12" t="n">
         <v>4</v>
@@ -2592,7 +2659,7 @@
         <v>8</v>
       </c>
       <c r="AO12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AP12" t="n">
         <v>23</v>
@@ -2613,7 +2680,7 @@
         <v>9</v>
       </c>
       <c r="AV12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW12" t="n">
         <v>20</v>
@@ -2625,7 +2692,7 @@
         <v>26</v>
       </c>
       <c r="AZ12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BA12" t="n">
         <v>15</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>5-8-2008-09</t>
+          <t>2009-05-08</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2820,7 @@
         <v>28</v>
       </c>
       <c r="AH13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI13" t="n">
         <v>25</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>5-8-2008-09</t>
+          <t>2009-05-08</t>
         </is>
       </c>
     </row>
@@ -2845,25 +2912,25 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E14" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F14" t="n">
         <v>17</v>
       </c>
       <c r="G14" t="n">
-        <v>0.79</v>
+        <v>0.793</v>
       </c>
       <c r="H14" t="n">
         <v>48.2</v>
       </c>
       <c r="I14" t="n">
-        <v>40.4</v>
+        <v>40.3</v>
       </c>
       <c r="J14" t="n">
-        <v>85.2</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="K14" t="n">
         <v>0.474</v>
@@ -2872,25 +2939,25 @@
         <v>6.7</v>
       </c>
       <c r="M14" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="N14" t="n">
-        <v>0.359</v>
+        <v>0.361</v>
       </c>
       <c r="O14" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="P14" t="n">
         <v>25.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.769</v>
+        <v>0.77</v>
       </c>
       <c r="R14" t="n">
         <v>12.4</v>
       </c>
       <c r="S14" t="n">
-        <v>31.4</v>
+        <v>31.5</v>
       </c>
       <c r="T14" t="n">
         <v>43.9</v>
@@ -2899,7 +2966,7 @@
         <v>23.3</v>
       </c>
       <c r="V14" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="W14" t="n">
         <v>8.800000000000001</v>
@@ -2911,19 +2978,19 @@
         <v>4.8</v>
       </c>
       <c r="Z14" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="AA14" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>107.1</v>
+        <v>106.9</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="AD14" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="AE14" t="n">
         <v>2</v>
@@ -2953,10 +3020,10 @@
         <v>15</v>
       </c>
       <c r="AN14" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AO14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP14" t="n">
         <v>8</v>
@@ -2968,7 +3035,7 @@
         <v>3</v>
       </c>
       <c r="AS14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AT14" t="n">
         <v>1</v>
@@ -2983,22 +3050,22 @@
         <v>2</v>
       </c>
       <c r="AX14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ14" t="n">
         <v>17</v>
       </c>
       <c r="BA14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB14" t="n">
         <v>3</v>
       </c>
       <c r="BC14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>5-8-2008-09</t>
+          <t>2009-05-08</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3202,7 @@
         <v>27</v>
       </c>
       <c r="AN15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO15" t="n">
         <v>13</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>5-8-2008-09</t>
+          <t>2009-05-08</t>
         </is>
       </c>
     </row>
@@ -3308,7 +3375,7 @@
         <v>15</v>
       </c>
       <c r="AK16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL16" t="n">
         <v>11</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>5-8-2008-09</t>
+          <t>2009-05-08</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E17" t="n">
         <v>34</v>
       </c>
       <c r="F17" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G17" t="n">
-        <v>0.42</v>
+        <v>0.415</v>
       </c>
       <c r="H17" t="n">
         <v>48.2</v>
@@ -3421,34 +3488,34 @@
         <v>17.2</v>
       </c>
       <c r="N17" t="n">
-        <v>0.362</v>
+        <v>0.363</v>
       </c>
       <c r="O17" t="n">
         <v>19.7</v>
       </c>
       <c r="P17" t="n">
-        <v>25.3</v>
+        <v>25.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.781</v>
+        <v>0.78</v>
       </c>
       <c r="R17" t="n">
         <v>11.9</v>
       </c>
       <c r="S17" t="n">
-        <v>29</v>
+        <v>28.9</v>
       </c>
       <c r="T17" t="n">
-        <v>40.8</v>
+        <v>40.7</v>
       </c>
       <c r="U17" t="n">
         <v>22</v>
       </c>
       <c r="V17" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="W17" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="X17" t="n">
         <v>3.8</v>
@@ -3457,7 +3524,7 @@
         <v>4.6</v>
       </c>
       <c r="Z17" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="AA17" t="n">
         <v>22.5</v>
@@ -3466,16 +3533,16 @@
         <v>99.3</v>
       </c>
       <c r="AC17" t="n">
-        <v>-0.9</v>
+        <v>-1.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="AE17" t="n">
         <v>20</v>
       </c>
       <c r="AF17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG17" t="n">
         <v>20</v>
@@ -3490,7 +3557,7 @@
         <v>8</v>
       </c>
       <c r="AK17" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL17" t="n">
         <v>21</v>
@@ -3505,7 +3572,7 @@
         <v>9</v>
       </c>
       <c r="AP17" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AQ17" t="n">
         <v>11</v>
@@ -3526,7 +3593,7 @@
         <v>14</v>
       </c>
       <c r="AW17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX17" t="n">
         <v>29</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>5-8-2008-09</t>
+          <t>2009-05-08</t>
         </is>
       </c>
     </row>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>5-8-2008-09</t>
+          <t>2009-05-08</t>
         </is>
       </c>
     </row>
@@ -3839,13 +3906,13 @@
         <v>20</v>
       </c>
       <c r="AF19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI19" t="n">
         <v>27</v>
@@ -3893,10 +3960,10 @@
         <v>24</v>
       </c>
       <c r="AX19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ19" t="n">
         <v>24</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>5-8-2008-09</t>
+          <t>2009-05-08</t>
         </is>
       </c>
     </row>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>5-8-2008-09</t>
+          <t>2009-05-08</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4285,7 @@
         <v>1</v>
       </c>
       <c r="AK21" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL21" t="n">
         <v>1</v>
@@ -4227,7 +4294,7 @@
         <v>1</v>
       </c>
       <c r="AN21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO21" t="n">
         <v>24</v>
@@ -4245,7 +4312,7 @@
         <v>9</v>
       </c>
       <c r="AT21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AU21" t="n">
         <v>11</v>
@@ -4254,7 +4321,7 @@
         <v>18</v>
       </c>
       <c r="AW21" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AX21" t="n">
         <v>30</v>
@@ -4263,7 +4330,7 @@
         <v>24</v>
       </c>
       <c r="AZ21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA21" t="n">
         <v>29</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>5-8-2008-09</t>
+          <t>2009-05-08</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4479,7 @@
         <v>28</v>
       </c>
       <c r="AO22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AP22" t="n">
         <v>12</v>
@@ -4430,7 +4497,7 @@
         <v>6</v>
       </c>
       <c r="AU22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AV22" t="n">
         <v>30</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>5-8-2008-09</t>
+          <t>2009-05-08</t>
         </is>
       </c>
     </row>
@@ -4582,7 +4649,7 @@
         <v>26</v>
       </c>
       <c r="AK23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL23" t="n">
         <v>2</v>
@@ -4594,7 +4661,7 @@
         <v>7</v>
       </c>
       <c r="AO23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AP23" t="n">
         <v>4</v>
@@ -4633,7 +4700,7 @@
         <v>6</v>
       </c>
       <c r="BB23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BC23" t="n">
         <v>4</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>5-8-2008-09</t>
+          <t>2009-05-08</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>5-8-2008-09</t>
+          <t>2009-05-08</t>
         </is>
       </c>
     </row>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>5-8-2008-09</t>
+          <t>2009-05-08</t>
         </is>
       </c>
     </row>
@@ -5029,46 +5096,46 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E26" t="n">
         <v>54</v>
       </c>
       <c r="F26" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G26" t="n">
-        <v>0.667</v>
+        <v>0.659</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
       </c>
       <c r="I26" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="J26" t="n">
-        <v>79.09999999999999</v>
+        <v>79.2</v>
       </c>
       <c r="K26" t="n">
-        <v>0.466</v>
+        <v>0.465</v>
       </c>
       <c r="L26" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="M26" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="N26" t="n">
         <v>0.383</v>
       </c>
       <c r="O26" t="n">
-        <v>18.7</v>
+        <v>18.5</v>
       </c>
       <c r="P26" t="n">
-        <v>24.4</v>
+        <v>24.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.766</v>
+        <v>0.765</v>
       </c>
       <c r="R26" t="n">
         <v>12.9</v>
@@ -5098,16 +5165,16 @@
         <v>20.4</v>
       </c>
       <c r="AA26" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="AB26" t="n">
-        <v>99.7</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="AC26" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="AD26" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="AE26" t="n">
         <v>5</v>
@@ -5128,7 +5195,7 @@
         <v>23</v>
       </c>
       <c r="AK26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL26" t="n">
         <v>9</v>
@@ -5140,13 +5207,13 @@
         <v>4</v>
       </c>
       <c r="AO26" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AP26" t="n">
         <v>16</v>
       </c>
       <c r="AQ26" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AR26" t="n">
         <v>1</v>
@@ -5155,7 +5222,7 @@
         <v>27</v>
       </c>
       <c r="AT26" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AU26" t="n">
         <v>19</v>
@@ -5173,10 +5240,10 @@
         <v>3</v>
       </c>
       <c r="AZ26" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BB26" t="n">
         <v>14</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>5-8-2008-09</t>
+          <t>2009-05-08</t>
         </is>
       </c>
     </row>
@@ -5358,7 +5425,7 @@
         <v>29</v>
       </c>
       <c r="BA27" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BB27" t="n">
         <v>12</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>5-8-2008-09</t>
+          <t>2009-05-08</t>
         </is>
       </c>
     </row>
@@ -5477,10 +5544,10 @@
         <v>5</v>
       </c>
       <c r="AF28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH28" t="n">
         <v>4</v>
@@ -5492,7 +5559,7 @@
         <v>19</v>
       </c>
       <c r="AK28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL28" t="n">
         <v>6</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>5-8-2008-09</t>
+          <t>2009-05-08</t>
         </is>
       </c>
     </row>
@@ -5713,7 +5780,7 @@
         <v>27</v>
       </c>
       <c r="AX29" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AY29" t="n">
         <v>12</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>5-8-2008-09</t>
+          <t>2009-05-08</t>
         </is>
       </c>
     </row>
@@ -5847,7 +5914,7 @@
         <v>11</v>
       </c>
       <c r="AH30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI30" t="n">
         <v>6</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>5-8-2008-09</t>
+          <t>2009-05-08</t>
         </is>
       </c>
     </row>
@@ -6056,7 +6123,7 @@
         <v>20</v>
       </c>
       <c r="AQ31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR31" t="n">
         <v>8</v>
@@ -6074,7 +6141,7 @@
         <v>13</v>
       </c>
       <c r="AW31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX31" t="n">
         <v>23</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>5-8-2008-09</t>
+          <t>2009-05-08</t>
         </is>
       </c>
     </row>
